--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:29:42+00:00</t>
+    <t>2025-03-17T15:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17T15:05:50+00:00</t>
+    <t>2025-03-18T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:04:30+00:00</t>
+    <t>2025-03-20T11:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T11:13:27+00:00</t>
+    <t>2025-03-20T15:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T15:00:12+00:00</t>
+    <t>2025-03-24T10:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:58:19+00:00</t>
+    <t>2025-03-24T11:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:08+00:00</t>
+    <t>2025-03-24T12:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T12:21:29+00:00</t>
+    <t>2025-03-26T10:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="476">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-26T10:25:04+00:00</t>
+    <t>2025-04-17T09:39:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1389,6 +1389,22 @@
   </si>
   <si>
     <t>Questionnaire.item.answerOption.extension</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.answerOption.extension:answerOptionAdditionalCode</t>
+  </si>
+  <si>
+    <t>answerOptionAdditionalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/AnswerOptionAdditionalCode}
+</t>
+  </si>
+  <si>
+    <t>AnswerOption Additional Code</t>
+  </si>
+  <si>
+    <t>An additional code for an option in a choice question</t>
   </si>
   <si>
     <t>Questionnaire.item.answerOption.modifierExtension</t>
@@ -1798,20 +1814,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO67"/>
+  <dimension ref="A1:AO68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.16796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.16796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.92578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.9921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.15234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.7578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.6953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1820,27 +1836,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="86.3125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.6953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.5390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="73.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.04296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="125.9375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="48.05859375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="107.96875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8553,7 +8569,7 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8575,14 +8591,12 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>136</v>
+        <v>319</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8619,16 +8633,14 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>323</v>
@@ -8649,7 +8661,7 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>82</v>
@@ -8666,11 +8678,13 @@
         <v>439</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="D59" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8683,26 +8697,22 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>135</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>332</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -8750,7 +8760,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8759,7 +8769,7 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>140</v>
@@ -8768,7 +8778,7 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>82</v>
@@ -8782,44 +8792,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>441</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>442</v>
+        <v>332</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>443</v>
+        <v>333</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -8843,13 +8855,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -8867,25 +8879,25 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>334</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>370</v>
+        <v>132</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>82</v>
@@ -8910,7 +8922,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>89</v>
@@ -8925,24 +8937,22 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>201</v>
+        <v>446</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>449</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>82</v>
       </c>
@@ -8962,13 +8972,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -8989,7 +8999,7 @@
         <v>445</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>89</v>
@@ -9032,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9044,7 +9054,7 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>306</v>
+        <v>201</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>451</v>
@@ -9055,13 +9065,13 @@
       <c r="N62" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="O62" t="s" s="2">
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="P62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9111,10 +9121,10 @@
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>101</v>
@@ -9137,10 +9147,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9151,7 +9161,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9163,16 +9173,20 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>164</v>
+        <v>306</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>314</v>
+        <v>456</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9220,25 +9234,25 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>316</v>
+        <v>455</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>317</v>
+        <v>370</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9252,21 +9266,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9278,17 +9292,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9337,19 +9349,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9369,14 +9381,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>331</v>
+        <v>134</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9389,26 +9401,24 @@
         <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O65" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9456,7 +9466,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9474,7 +9484,7 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>132</v>
+        <v>317</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
@@ -9488,44 +9498,46 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>460</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>461</v>
+        <v>332</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>462</v>
+        <v>333</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -9549,13 +9561,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -9573,25 +9585,25 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>459</v>
+        <v>334</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>370</v>
+        <v>132</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
@@ -9616,10 +9628,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -9631,20 +9643,18 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O67" t="s" s="2">
         <v>468</v>
       </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -9668,13 +9678,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -9695,13 +9705,13 @@
         <v>464</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>101</v>
@@ -9710,15 +9720,134 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO67" t="s" s="2">
+      <c r="M68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/sandbox/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:39:14+00:00</t>
+    <t>2025-04-17T11:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
